--- a/AAII_Financials/Yearly/SGML_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SGML_YR_FIN.xlsx
@@ -2700,7 +2700,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14800</v>
+        <v>20400</v>
       </c>
       <c r="E61" s="3">
         <v>113400</v>
@@ -2742,7 +2742,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>21900</v>
+        <v>16200</v>
       </c>
       <c r="E62" s="3">
         <v>12600</v>
